--- a/学习计划/三个月学习大纲计划.xlsx
+++ b/学习计划/三个月学习大纲计划.xlsx
@@ -3030,7 +3030,7 @@
         <v>8</v>
       </c>
       <c r="C3" s="10">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D3" s="10" t="s">
         <v>9</v>
@@ -3044,7 +3044,7 @@
         <v>11</v>
       </c>
       <c r="C4" s="11">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D4" s="11" t="s">
         <v>12</v>
